--- a/Result/profitability/3556.xlsx
+++ b/Result/profitability/3556.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.73</v>
       </c>
       <c r="M2" t="n">
-        <v>0.61</v>
+        <v>0.725</v>
       </c>
       <c r="N2" t="n">
-        <v>48.47375</v>
+        <v>48.79125000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.51</v>
       </c>
       <c r="M3" t="n">
-        <v>0.64</v>
+        <v>0.7212499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>49.62625</v>
+        <v>49.76875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.49</v>
       </c>
       <c r="M4" t="n">
-        <v>0.63375</v>
+        <v>0.73125</v>
       </c>
       <c r="N4" t="n">
-        <v>49.7725</v>
+        <v>49.97625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>0.60375</v>
+        <v>0.6974999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>50.07375</v>
+        <v>50.31375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.47</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6074999999999999</v>
+        <v>0.70125</v>
       </c>
       <c r="N6" t="n">
-        <v>51.73375</v>
+        <v>52.54125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.75</v>
       </c>
       <c r="M7" t="n">
-        <v>0.64625</v>
+        <v>0.6875</v>
       </c>
       <c r="N7" t="n">
-        <v>54.06875</v>
+        <v>53.94875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1394,7 +1394,7 @@
         <v>0.61375</v>
       </c>
       <c r="N8" t="n">
-        <v>55.2775</v>
+        <v>55.3225</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>0.595</v>
       </c>
       <c r="N12" t="n">
-        <v>56.65000000000001</v>
+        <v>56.65</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3556</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>319</v>
+      </c>
+      <c r="D75" t="n">
+        <v>161</v>
+      </c>
+      <c r="E75" t="n">
+        <v>159</v>
+      </c>
+      <c r="F75" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="G75" t="n">
+        <v>59</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>18.34%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>30</v>
+      </c>
+      <c r="J75" t="n">
+        <v>88</v>
+      </c>
+      <c r="K75" t="n">
+        <v>76</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6675</v>
+      </c>
+      <c r="N75" t="n">
+        <v>48.06375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.3599999999999994</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.007296311309282544</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.704545454545455</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.920000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.04018417748011727</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
